--- a/Result/profitability/6275.xlsx
+++ b/Result/profitability/6275.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.28</v>
       </c>
       <c r="M2" t="n">
-        <v>0.64875</v>
+        <v>0.6112500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>19.10625</v>
+        <v>18.9</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0.55125</v>
+        <v>0.51</v>
       </c>
       <c r="N3" t="n">
-        <v>19.14</v>
+        <v>19.2025</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4425000000000001</v>
+        <v>0.4412500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>19.5425</v>
+        <v>19.55125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3525</v>
+        <v>0.32375</v>
       </c>
       <c r="N5" t="n">
-        <v>19.7125</v>
+        <v>19.8975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2187500000000001</v>
+        <v>0.1825000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>19.46</v>
+        <v>19.36125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09875000000000006</v>
+        <v>0.05750000000000006</v>
       </c>
       <c r="N7" t="n">
-        <v>19.40125</v>
+        <v>19.205</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.02</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.001249999999999941</v>
+        <v>6.028164079019405e-17</v>
       </c>
       <c r="N8" t="n">
-        <v>19.62375</v>
+        <v>19.70125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6275</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D75" t="n">
+        <v>860</v>
+      </c>
+      <c r="E75" t="n">
+        <v>192</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="G75" t="n">
+        <v>36</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>12</v>
+      </c>
+      <c r="J75" t="n">
+        <v>47</v>
+      </c>
+      <c r="K75" t="n">
+        <v>39</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.3875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.02083333333333326</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.6199999999999974</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03522727272727266</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3194444444444444</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08841099163679811</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
